--- a/data/1/6.3 fig1 p 10.xlsx
+++ b/data/1/6.3 fig1 p 10.xlsx
@@ -1273,13 +1273,13 @@
         <v>5</v>
       </c>
       <c r="C2">
-        <v>7.74</v>
+        <v>8.24</v>
       </c>
       <c r="D2">
-        <v>7.74</v>
+        <v>8.24</v>
       </c>
       <c r="E2">
-        <v>7.74</v>
+        <v>8.24</v>
       </c>
       <c r="F2">
         <v>7.45</v>
@@ -1300,13 +1300,13 @@
         <v>7.39</v>
       </c>
       <c r="L2">
-        <v>7.6</v>
+        <v>8.16</v>
       </c>
       <c r="M2">
-        <v>7.6</v>
+        <v>8.16</v>
       </c>
       <c r="N2">
-        <v>7.6</v>
+        <v>8.16</v>
       </c>
       <c r="O2">
         <v>8.17</v>
@@ -1917,49 +1917,49 @@
         <v>6</v>
       </c>
       <c r="C17">
-        <v>8.2</v>
+        <v>7.7</v>
       </c>
       <c r="D17">
-        <v>8.35</v>
+        <v>7.8</v>
       </c>
       <c r="E17">
-        <v>8.3</v>
+        <v>8</v>
       </c>
       <c r="F17">
-        <v>7.74</v>
+        <v>6.74</v>
       </c>
       <c r="G17">
-        <v>7.8</v>
+        <v>6.8</v>
       </c>
       <c r="H17">
+        <v>6.78</v>
+      </c>
+      <c r="I17">
+        <v>5.7</v>
+      </c>
+      <c r="J17">
+        <v>5.7</v>
+      </c>
+      <c r="K17">
+        <v>5.44</v>
+      </c>
+      <c r="L17">
+        <v>7.66</v>
+      </c>
+      <c r="M17">
         <v>7.78</v>
       </c>
-      <c r="I17">
-        <v>7.23</v>
-      </c>
-      <c r="J17">
-        <v>7.27</v>
-      </c>
-      <c r="K17">
-        <v>7.44</v>
-      </c>
-      <c r="L17">
-        <v>8.16</v>
-      </c>
-      <c r="M17">
+      <c r="N17">
+        <v>7.79</v>
+      </c>
+      <c r="O17">
+        <v>8</v>
+      </c>
+      <c r="P17">
         <v>8.28</v>
       </c>
-      <c r="N17">
-        <v>8.29</v>
-      </c>
-      <c r="O17">
-        <v>8.64</v>
-      </c>
-      <c r="P17">
-        <v>8.68</v>
-      </c>
       <c r="Q17">
-        <v>8.67</v>
+        <v>8.17</v>
       </c>
     </row>
     <row r="18" spans="1:17">
@@ -1967,49 +1967,49 @@
         <v>7</v>
       </c>
       <c r="C18">
-        <v>9.26</v>
+        <v>8.86</v>
       </c>
       <c r="D18">
-        <v>9.17</v>
+        <v>8.57</v>
       </c>
       <c r="E18">
-        <v>9.23</v>
+        <v>8.63</v>
       </c>
       <c r="F18">
-        <v>8.6</v>
+        <v>7.6</v>
       </c>
       <c r="G18">
-        <v>8.58</v>
+        <v>7.58</v>
       </c>
       <c r="H18">
-        <v>8.4</v>
+        <v>7.4</v>
       </c>
       <c r="I18">
         <v>6.98</v>
       </c>
       <c r="J18">
-        <v>7.33</v>
+        <v>7</v>
       </c>
       <c r="K18">
-        <v>7.37</v>
+        <v>7</v>
       </c>
       <c r="L18">
-        <v>8.64</v>
+        <v>8.14</v>
       </c>
       <c r="M18">
-        <v>8.81</v>
+        <v>8.21</v>
       </c>
       <c r="N18">
-        <v>8.64</v>
+        <v>8.24</v>
       </c>
       <c r="O18">
-        <v>9.4</v>
+        <v>8.9</v>
       </c>
       <c r="P18">
-        <v>9.57</v>
+        <v>8.8</v>
       </c>
       <c r="Q18">
-        <v>9.33</v>
+        <v>9.03</v>
       </c>
     </row>
     <row r="19" spans="1:17">
@@ -2020,13 +2020,13 @@
         <v>8.9</v>
       </c>
       <c r="D19">
-        <v>9.01</v>
+        <v>8.81</v>
       </c>
       <c r="E19">
-        <v>9.22</v>
+        <v>8.92</v>
       </c>
       <c r="F19">
-        <v>9.79</v>
+        <v>9.49</v>
       </c>
       <c r="G19">
         <v>9.66</v>
@@ -2035,31 +2035,31 @@
         <v>9.69</v>
       </c>
       <c r="I19">
-        <v>5.58</v>
+        <v>6.08</v>
       </c>
       <c r="J19">
-        <v>5.28</v>
+        <v>6.28</v>
       </c>
       <c r="K19">
-        <v>5.32</v>
+        <v>6.32</v>
       </c>
       <c r="L19">
-        <v>8.84</v>
+        <v>8.34</v>
       </c>
       <c r="M19">
-        <v>8.72</v>
+        <v>8.32</v>
       </c>
       <c r="N19">
-        <v>8.65</v>
+        <v>8.45</v>
       </c>
       <c r="O19">
         <v>9.79</v>
       </c>
       <c r="P19">
-        <v>10.05</v>
+        <v>9.5</v>
       </c>
       <c r="Q19">
-        <v>9.92</v>
+        <v>9.5</v>
       </c>
     </row>
     <row r="20" spans="1:17">
@@ -2067,49 +2067,49 @@
         <v>9</v>
       </c>
       <c r="C20">
-        <v>8.91</v>
+        <v>8.41</v>
       </c>
       <c r="D20">
-        <v>9.07</v>
+        <v>8.56</v>
       </c>
       <c r="E20">
-        <v>9.07</v>
+        <v>8.77</v>
       </c>
       <c r="F20">
-        <v>9.67</v>
+        <v>9.47</v>
       </c>
       <c r="G20">
-        <v>9.76</v>
+        <v>9.36</v>
       </c>
       <c r="H20">
-        <v>9.81</v>
+        <v>9.51</v>
       </c>
       <c r="I20">
-        <v>6.83</v>
+        <v>5.83</v>
       </c>
       <c r="J20">
-        <v>7.05</v>
+        <v>6</v>
       </c>
       <c r="K20">
-        <v>6.78</v>
+        <v>5.78</v>
       </c>
       <c r="L20">
-        <v>8.74</v>
+        <v>8.24</v>
       </c>
       <c r="M20">
-        <v>8.72</v>
+        <v>8.02</v>
       </c>
       <c r="N20">
-        <v>8.72</v>
+        <v>8.12</v>
       </c>
       <c r="O20">
-        <v>9.92</v>
+        <v>9.7</v>
       </c>
       <c r="P20">
-        <v>9.97</v>
+        <v>9.7</v>
       </c>
       <c r="Q20">
-        <v>9.99</v>
+        <v>9.69</v>
       </c>
     </row>
     <row r="22" spans="1:17">
@@ -2235,10 +2235,10 @@
         <v>5.86</v>
       </c>
       <c r="J24">
-        <v>6.35</v>
+        <v>5.35</v>
       </c>
       <c r="K24">
-        <v>5.14</v>
+        <v>5.54</v>
       </c>
       <c r="L24">
         <v>7.78</v>
@@ -2282,13 +2282,13 @@
         <v>7.9</v>
       </c>
       <c r="I25">
-        <v>4.98</v>
+        <v>6.98</v>
       </c>
       <c r="J25">
-        <v>5.2</v>
+        <v>6.7</v>
       </c>
       <c r="K25">
-        <v>4.98</v>
+        <v>6.98</v>
       </c>
       <c r="L25">
         <v>8.17</v>
@@ -2332,13 +2332,13 @@
         <v>9.13</v>
       </c>
       <c r="I26">
-        <v>5.21</v>
+        <v>6.21</v>
       </c>
       <c r="J26">
-        <v>5.29</v>
+        <v>6.29</v>
       </c>
       <c r="K26">
-        <v>5.4</v>
+        <v>6</v>
       </c>
       <c r="L26">
         <v>8.28</v>
@@ -2382,22 +2382,22 @@
         <v>9.48</v>
       </c>
       <c r="I27">
-        <v>6.61</v>
+        <v>5.61</v>
       </c>
       <c r="J27">
-        <v>6.71</v>
+        <v>5.71</v>
       </c>
       <c r="K27">
-        <v>6.76</v>
+        <v>5.76</v>
       </c>
       <c r="L27">
-        <v>8.46</v>
+        <v>8</v>
       </c>
       <c r="M27">
-        <v>8.2</v>
+        <v>8.1</v>
       </c>
       <c r="N27">
-        <v>8.27</v>
+        <v>8.07</v>
       </c>
       <c r="O27">
         <v>9.43</v>
